--- a/master/employees.xlsx
+++ b/master/employees.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,86 +417,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>emp_code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate_plan</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rate_mode</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fix_rate</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cond_free_first_n</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cond_after_fix_rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cond_pay_type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>scoring_mode</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>scoring_fix</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -540,7 +528,7 @@
           <t>ธนาวุธ แก้วดำ</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>43937</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -602,7 +590,7 @@
           <t>สุมาพร เอมรักษา</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>45297</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -663,7 +651,7 @@
           <t>ชยพล ภาวงศ์</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -721,7 +709,7 @@
           <t>ศุภลักษณ์ วิภาสจรรโลง</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>45964</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -785,7 +773,7 @@
           <t>จิตราวดี เวชกามา</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -848,7 +836,7 @@
           <t>ชัยวัฒน์ พระจันทร์</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -911,7 +899,7 @@
           <t>สาวิตรี ดอนกิ่ง</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>45300</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -971,7 +959,7 @@
           <t>นันทพงศ์ พัดไธสง</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -1031,7 +1019,7 @@
           <t>วรวัฒน์ ลี้วงศ์วัฒนา</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -1087,7 +1075,7 @@
           <t>ยุวดี ยอดแบน</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -1141,7 +1129,7 @@
           <t>นาบีละห์ ดาโอะ</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="1" t="n">
         <v>45783</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -1195,7 +1183,7 @@
           <t>อมรรัตน์ เดชพละ</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="1" t="n">
         <v>45783</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -1249,7 +1237,7 @@
           <t>ธมนวรรณ เมืองพา</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -1305,7 +1293,7 @@
           <t>วนัชพร ฤทธิวาจา</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -1361,7 +1349,7 @@
           <t>อาณกร สิริบำรุงเมือง</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -1417,7 +1405,7 @@
           <t>อนงค์ ภูมิศักดิ์</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -1473,7 +1461,7 @@
           <t>ธนิสรา โฉมมิตร</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -1527,7 +1515,7 @@
           <t>วัชราภรณ์ บุดดา</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -1581,7 +1569,7 @@
           <t>วรัญญา เสาวัง</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -1637,7 +1625,7 @@
           <t>กชกร ชูศิลป์กิจเจริญ</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -1691,7 +1679,7 @@
           <t>คฑาวุธ ก่อเผ่าพานิช</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -1745,7 +1733,7 @@
           <t>นรินทร์ทิพย์ นวลแก้ว</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -1799,7 +1787,7 @@
           <t>เสาวลักษณ์ แปลงนวล</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -1853,7 +1841,7 @@
           <t>ปริวรรต เกิดมงคล</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -1915,7 +1903,7 @@
           <t>พัชรินทร์ กล้าหาญ</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -1977,7 +1965,7 @@
           <t>จิระพล พร้อมจิต</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="1" t="n">
         <v>45797</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -2037,7 +2025,7 @@
           <t>ประภาพร แสนอิว</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="1" t="n">
         <v>45915</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -2097,7 +2085,7 @@
           <t>วริศรา แป้นเพชร</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="1" t="n">
         <v>45955</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -2157,7 +2145,7 @@
           <t>จิตมณี ลีงอย</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="1" t="n">
         <v>45666</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -2217,7 +2205,7 @@
           <t>ราฟา อภิวัฒนะโภคิน</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="G31" t="inlineStr">
@@ -2279,7 +2267,7 @@
           <t>ธัญทิศา พุฒแก้ว</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="G32" t="inlineStr">
@@ -2339,7 +2327,7 @@
           <t>สุมาลี ผลพวก</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -2401,7 +2389,7 @@
           <t>ณัฐรินทร์ สุขสม</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -2461,7 +2449,7 @@
           <t>ธนาวุธ แก้วดำ</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -2519,7 +2507,7 @@
           <t>Kantanop Chusuwan</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -2577,7 +2565,7 @@
           <t>Thidarat Kaewkamkong</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -2635,7 +2623,7 @@
           <t>Rungthiwa Joomsimma</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G38" t="inlineStr">
@@ -2693,7 +2681,7 @@
           <t>Somruethai Sukhajorn</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -2751,7 +2739,7 @@
           <t>Vijitra Burapratheep</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -2809,7 +2797,7 @@
           <t>สุมาลี ผลพวก</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -2871,7 +2859,7 @@
           <t>สุนิชญา เดชพลกรัง</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -2933,7 +2921,7 @@
           <t>Worrapan Jantra</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G43" t="inlineStr">
@@ -2995,7 +2983,7 @@
           <t>Supang Infaktha</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -3053,7 +3041,7 @@
           <t>วฤทธิ์ นามจริง</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -3083,11 +3071,7 @@
       <c r="O45" t="b">
         <v>1</v>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3115,7 +3099,7 @@
           <t>Phanupong Tengthong</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -3173,7 +3157,7 @@
           <t>อนงค์ ภูมิภักดิ์</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="1" t="n">
         <v>45852</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -3203,6 +3187,164 @@
       </c>
       <c r="P47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>E047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>test test</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>test test</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>E048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>test2 test</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>test2 test</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>E049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>test3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>test3 test</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>test3 test</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
